--- a/conteo.xlsx
+++ b/conteo.xlsx
@@ -314,7 +314,7 @@
         <v>10.0</v>
       </c>
       <c r="B2" s="3">
-        <v>46286.27569444444</v>
+        <v>46293.28472222222</v>
       </c>
       <c r="C2" s="2">
         <v>1.0</v>
@@ -334,7 +334,7 @@
         <v>9.0</v>
       </c>
       <c r="B3" s="3">
-        <v>46286.30902777778</v>
+        <v>46293.31736111111</v>
       </c>
       <c r="C3" s="2">
         <v>1.0</v>
@@ -354,7 +354,7 @@
         <v>6.0</v>
       </c>
       <c r="B4" s="3">
-        <v>46286.370833333334</v>
+        <v>46293.379166666666</v>
       </c>
       <c r="C4" s="2">
         <v>1.0</v>
@@ -374,7 +374,7 @@
         <v>17.0</v>
       </c>
       <c r="B5" s="3">
-        <v>46286.39722222222</v>
+        <v>46293.40694444445</v>
       </c>
       <c r="C5" s="2">
         <v>1.0</v>
@@ -394,7 +394,7 @@
         <v>6.0</v>
       </c>
       <c r="B6" s="3">
-        <v>46286.40555555555</v>
+        <v>46293.415972222225</v>
       </c>
       <c r="C6" s="2">
         <v>1.0</v>
@@ -414,7 +414,7 @@
         <v>5.0</v>
       </c>
       <c r="B7" s="3">
-        <v>46286.410416666666</v>
+        <v>46293.416666666664</v>
       </c>
       <c r="C7" s="2">
         <v>1.0</v>
@@ -431,10 +431,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2">
-        <v>15.0</v>
+        <v>5.0</v>
       </c>
       <c r="B8" s="3">
-        <v>46286.415972222225</v>
+        <v>46293.416666666664</v>
       </c>
       <c r="C8" s="2">
         <v>1.0</v>
@@ -451,16 +451,16 @@
     </row>
     <row r="9">
       <c r="A9" s="2">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="B9" s="3">
-        <v>46286.45208333333</v>
+        <v>46293.419444444444</v>
       </c>
       <c r="C9" s="2">
         <v>1.0</v>
       </c>
       <c r="D9" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="E9" s="2">
         <v>1.0</v>
@@ -471,10 +471,10 @@
     </row>
     <row r="10">
       <c r="A10" s="2">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="B10" s="3">
-        <v>46286.470138888886</v>
+        <v>46293.458333333336</v>
       </c>
       <c r="C10" s="2">
         <v>1.0</v>
@@ -491,10 +491,10 @@
     </row>
     <row r="11">
       <c r="A11" s="2">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="B11" s="3">
-        <v>46286.47222222222</v>
+        <v>46293.47708333333</v>
       </c>
       <c r="C11" s="2">
         <v>1.0</v>
@@ -511,10 +511,10 @@
     </row>
     <row r="12">
       <c r="A12" s="2">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="B12" s="3">
-        <v>46286.47430555556</v>
+        <v>46293.479166666664</v>
       </c>
       <c r="C12" s="2">
         <v>1.0</v>
@@ -531,16 +531,16 @@
     </row>
     <row r="13">
       <c r="A13" s="2">
-        <v>12.0</v>
+        <v>5.0</v>
       </c>
       <c r="B13" s="3">
-        <v>46286.489583333336</v>
+        <v>46293.48055555556</v>
       </c>
       <c r="C13" s="2">
         <v>1.0</v>
       </c>
       <c r="D13" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="E13" s="2">
         <v>1.0</v>
@@ -551,10 +551,10 @@
     </row>
     <row r="14">
       <c r="A14" s="2">
-        <v>5.0</v>
+        <v>12.0</v>
       </c>
       <c r="B14" s="3">
-        <v>46286.53055555555</v>
+        <v>46293.493055555555</v>
       </c>
       <c r="C14" s="2">
         <v>1.0</v>
@@ -574,7 +574,7 @@
         <v>5.0</v>
       </c>
       <c r="B15" s="3">
-        <v>46286.53055555555</v>
+        <v>46293.53125</v>
       </c>
       <c r="C15" s="2">
         <v>1.0</v>
@@ -591,16 +591,16 @@
     </row>
     <row r="16">
       <c r="A16" s="2">
-        <v>12.0</v>
+        <v>5.0</v>
       </c>
       <c r="B16" s="3">
-        <v>46286.53402777778</v>
+        <v>46293.53125</v>
       </c>
       <c r="C16" s="2">
         <v>1.0</v>
       </c>
       <c r="D16" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="E16" s="2">
         <v>1.0</v>
@@ -611,10 +611,10 @@
     </row>
     <row r="17">
       <c r="A17" s="2">
-        <v>17.0</v>
+        <v>12.0</v>
       </c>
       <c r="B17" s="3">
-        <v>46286.57986111111</v>
+        <v>46293.541666666664</v>
       </c>
       <c r="C17" s="2">
         <v>1.0</v>
@@ -631,10 +631,10 @@
     </row>
     <row r="18">
       <c r="A18" s="2">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="B18" s="3">
-        <v>46286.586805555555</v>
+        <v>46293.549305555556</v>
       </c>
       <c r="C18" s="2">
         <v>1.0</v>
@@ -651,10 +651,10 @@
     </row>
     <row r="19">
       <c r="A19" s="2">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="B19" s="3">
-        <v>46286.5875</v>
+        <v>46293.58611111111</v>
       </c>
       <c r="C19" s="2">
         <v>1.0</v>
@@ -671,16 +671,16 @@
     </row>
     <row r="20">
       <c r="A20" s="2">
-        <v>15.0</v>
+        <v>12.0</v>
       </c>
       <c r="B20" s="3">
-        <v>46286.5875</v>
+        <v>46293.600694444445</v>
       </c>
       <c r="C20" s="2">
         <v>1.0</v>
       </c>
       <c r="D20" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="E20" s="2">
         <v>1.0</v>
@@ -691,16 +691,16 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2">
-        <v>7.0</v>
+        <v>15.0</v>
       </c>
       <c r="B21" s="3">
-        <v>46286.59930555556</v>
+        <v>46293.600694444445</v>
       </c>
       <c r="C21" s="2">
         <v>1.0</v>
       </c>
       <c r="D21" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="E21" s="2">
         <v>1.0</v>
@@ -711,10 +711,10 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2">
-        <v>5.0</v>
+        <v>15.0</v>
       </c>
       <c r="B22" s="3">
-        <v>46286.60138888889</v>
+        <v>46293.600694444445</v>
       </c>
       <c r="C22" s="2">
         <v>1.0</v>
@@ -731,16 +731,16 @@
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2">
-        <v>13.0</v>
+        <v>5.0</v>
       </c>
       <c r="B23" s="3">
-        <v>46286.6375</v>
+        <v>46293.60555555556</v>
       </c>
       <c r="C23" s="2">
         <v>1.0</v>
       </c>
       <c r="D23" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="E23" s="2">
         <v>1.0</v>
@@ -751,16 +751,16 @@
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="B24" s="3">
-        <v>46286.65902777778</v>
+        <v>46293.60555555556</v>
       </c>
       <c r="C24" s="2">
         <v>1.0</v>
       </c>
       <c r="D24" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="E24" s="2">
         <v>1.0</v>
@@ -771,10 +771,10 @@
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="B25" s="3">
-        <v>46286.65972222222</v>
+        <v>46293.61319444444</v>
       </c>
       <c r="C25" s="2">
         <v>1.0</v>
@@ -791,10 +791,10 @@
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2">
-        <v>6.0</v>
+        <v>13.0</v>
       </c>
       <c r="B26" s="3">
-        <v>46286.66180555556</v>
+        <v>46293.64027777778</v>
       </c>
       <c r="C26" s="2">
         <v>1.0</v>
@@ -814,7 +814,7 @@
         <v>5.0</v>
       </c>
       <c r="B27" s="3">
-        <v>46286.68819444445</v>
+        <v>46293.66180555556</v>
       </c>
       <c r="C27" s="2">
         <v>1.0</v>
@@ -831,10 +831,10 @@
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2">
-        <v>19.0</v>
+        <v>2.0</v>
       </c>
       <c r="B28" s="3">
-        <v>46286.71875</v>
+        <v>46293.665972222225</v>
       </c>
       <c r="C28" s="2">
         <v>1.0</v>
@@ -851,16 +851,16 @@
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="2">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="B29" s="3">
-        <v>46286.71944444445</v>
+        <v>46293.66875</v>
       </c>
       <c r="C29" s="2">
         <v>1.0</v>
       </c>
       <c r="D29" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="E29" s="2">
         <v>1.0</v>
@@ -871,16 +871,16 @@
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="2">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="B30" s="3">
-        <v>46286.720138888886</v>
+        <v>46293.67222222222</v>
       </c>
       <c r="C30" s="2">
         <v>1.0</v>
       </c>
       <c r="D30" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="E30" s="2">
         <v>1.0</v>
@@ -891,16 +891,16 @@
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="B31" s="3">
-        <v>46286.720138888886</v>
+        <v>46293.675</v>
       </c>
       <c r="C31" s="2">
         <v>1.0</v>
       </c>
       <c r="D31" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="E31" s="2">
         <v>1.0</v>
@@ -911,16 +911,16 @@
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="2">
-        <v>7.0</v>
+        <v>11.0</v>
       </c>
       <c r="B32" s="3">
-        <v>46286.77222222222</v>
+        <v>46293.675</v>
       </c>
       <c r="C32" s="2">
         <v>1.0</v>
       </c>
       <c r="D32" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="E32" s="2">
         <v>1.0</v>
@@ -931,16 +931,16 @@
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="2">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
       <c r="B33" s="3">
-        <v>46286.790972222225</v>
+        <v>46293.67569444444</v>
       </c>
       <c r="C33" s="2">
         <v>1.0</v>
       </c>
       <c r="D33" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="E33" s="2">
         <v>1.0</v>
@@ -951,10 +951,10 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="2">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="B34" s="3">
-        <v>46286.868055555555</v>
+        <v>46293.70625</v>
       </c>
       <c r="C34" s="2">
         <v>1.0</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="2">
-        <v>10.0</v>
+        <v>19.0</v>
       </c>
       <c r="B35" s="3">
-        <v>46287.270833333336</v>
+        <v>46293.71319444444</v>
       </c>
       <c r="C35" s="2">
         <v>1.0</v>
@@ -991,16 +991,16 @@
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="2">
-        <v>12.0</v>
+        <v>6.0</v>
       </c>
       <c r="B36" s="3">
-        <v>46287.274305555555</v>
+        <v>46293.72361111111</v>
       </c>
       <c r="C36" s="2">
         <v>1.0</v>
       </c>
       <c r="D36" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="E36" s="2">
         <v>1.0</v>
@@ -1011,16 +1011,16 @@
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="2">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="B37" s="3">
-        <v>46287.274305555555</v>
+        <v>46293.72430555556</v>
       </c>
       <c r="C37" s="2">
         <v>1.0</v>
       </c>
       <c r="D37" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="E37" s="2">
         <v>1.0</v>
@@ -1031,16 +1031,16 @@
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="2">
-        <v>19.0</v>
+        <v>11.0</v>
       </c>
       <c r="B38" s="3">
-        <v>46287.29513888889</v>
+        <v>46293.725694444445</v>
       </c>
       <c r="C38" s="2">
         <v>1.0</v>
       </c>
       <c r="D38" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="E38" s="2">
         <v>1.0</v>
@@ -1051,16 +1051,16 @@
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="2">
-        <v>7.0</v>
+        <v>12.0</v>
       </c>
       <c r="B39" s="3">
-        <v>46287.3375</v>
+        <v>46293.72638888889</v>
       </c>
       <c r="C39" s="2">
         <v>1.0</v>
       </c>
       <c r="D39" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="E39" s="2">
         <v>1.0</v>
@@ -1071,16 +1071,16 @@
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="2">
-        <v>5.0</v>
+        <v>19.0</v>
       </c>
       <c r="B40" s="3">
-        <v>46287.37708333333</v>
+        <v>46293.78472222222</v>
       </c>
       <c r="C40" s="2">
         <v>1.0</v>
       </c>
       <c r="D40" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="E40" s="2">
         <v>1.0</v>
@@ -1091,16 +1091,16 @@
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="2">
-        <v>15.0</v>
+        <v>19.0</v>
       </c>
       <c r="B41" s="3">
-        <v>46287.40138888889</v>
+        <v>46293.785416666666</v>
       </c>
       <c r="C41" s="2">
         <v>1.0</v>
       </c>
       <c r="D41" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="E41" s="2">
         <v>1.0</v>
@@ -1111,10 +1111,10 @@
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="2">
-        <v>19.0</v>
+        <v>7.0</v>
       </c>
       <c r="B42" s="3">
-        <v>46287.407638888886</v>
+        <v>46293.788194444445</v>
       </c>
       <c r="C42" s="2">
         <v>1.0</v>
@@ -1131,16 +1131,16 @@
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="2">
-        <v>17.0</v>
+        <v>1.0</v>
       </c>
       <c r="B43" s="3">
-        <v>46287.410416666666</v>
+        <v>46293.8375</v>
       </c>
       <c r="C43" s="2">
         <v>1.0</v>
       </c>
       <c r="D43" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="E43" s="2">
         <v>1.0</v>
@@ -1151,10 +1151,10 @@
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="2">
-        <v>5.0</v>
+        <v>13.0</v>
       </c>
       <c r="B44" s="3">
-        <v>46287.413194444445</v>
+        <v>46293.85486111111</v>
       </c>
       <c r="C44" s="2">
         <v>1.0</v>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="2">
-        <v>19.0</v>
+        <v>10.0</v>
       </c>
       <c r="B45" s="3">
-        <v>46287.441666666666</v>
+        <v>46294.274305555555</v>
       </c>
       <c r="C45" s="2">
         <v>1.0</v>
@@ -1191,16 +1191,16 @@
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="2">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="B46" s="3">
-        <v>46287.45763888889</v>
+        <v>46294.28055555555</v>
       </c>
       <c r="C46" s="2">
         <v>1.0</v>
       </c>
       <c r="D46" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="E46" s="2">
         <v>1.0</v>
@@ -1211,10 +1211,10 @@
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="2">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="B47" s="3">
-        <v>46287.47222222222</v>
+        <v>46294.33472222222</v>
       </c>
       <c r="C47" s="2">
         <v>1.0</v>
@@ -1231,16 +1231,16 @@
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="2">
-        <v>12.0</v>
+        <v>19.0</v>
       </c>
       <c r="B48" s="3">
-        <v>46287.478472222225</v>
+        <v>46294.34444444445</v>
       </c>
       <c r="C48" s="2">
         <v>1.0</v>
       </c>
       <c r="D48" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="E48" s="2">
         <v>1.0</v>
@@ -1251,10 +1251,10 @@
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="2">
-        <v>9.0</v>
+        <v>17.0</v>
       </c>
       <c r="B49" s="3">
-        <v>46287.49930555555</v>
+        <v>46294.39791666667</v>
       </c>
       <c r="C49" s="2">
         <v>1.0</v>
@@ -1271,16 +1271,16 @@
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="2">
-        <v>7.0</v>
+        <v>15.0</v>
       </c>
       <c r="B50" s="3">
-        <v>46287.509722222225</v>
+        <v>46294.42152777778</v>
       </c>
       <c r="C50" s="2">
         <v>1.0</v>
       </c>
       <c r="D50" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="E50" s="2">
         <v>1.0</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="2">
-        <v>19.0</v>
+        <v>10.0</v>
       </c>
       <c r="B51" s="3">
-        <v>46287.52569444444</v>
+        <v>46294.459027777775</v>
       </c>
       <c r="C51" s="2">
         <v>1.0</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="2">
-        <v>15.0</v>
+        <v>12.0</v>
       </c>
       <c r="B52" s="3">
-        <v>46287.53125</v>
+        <v>46294.459027777775</v>
       </c>
       <c r="C52" s="2">
         <v>1.0</v>
@@ -1331,10 +1331,10 @@
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="2">
-        <v>17.0</v>
+        <v>7.0</v>
       </c>
       <c r="B53" s="3">
-        <v>46287.57847222222</v>
+        <v>46294.46111111111</v>
       </c>
       <c r="C53" s="2">
         <v>1.0</v>
@@ -1351,10 +1351,10 @@
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="2">
-        <v>13.0</v>
+        <v>9.0</v>
       </c>
       <c r="B54" s="3">
-        <v>46287.63402777778</v>
+        <v>46294.5</v>
       </c>
       <c r="C54" s="2">
         <v>1.0</v>
@@ -1371,16 +1371,16 @@
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="2">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="B55" s="3">
-        <v>46287.6375</v>
+        <v>46294.50069444445</v>
       </c>
       <c r="C55" s="2">
         <v>1.0</v>
       </c>
       <c r="D55" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="E55" s="2">
         <v>1.0</v>
@@ -1391,10 +1391,10 @@
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="2">
-        <v>1.0</v>
+        <v>11.0</v>
       </c>
       <c r="B56" s="3">
-        <v>46287.65694444445</v>
+        <v>46294.50208333333</v>
       </c>
       <c r="C56" s="2">
         <v>1.0</v>
@@ -1411,10 +1411,10 @@
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="2">
-        <v>15.0</v>
+        <v>7.0</v>
       </c>
       <c r="B57" s="3">
-        <v>46287.65833333333</v>
+        <v>46294.52777777778</v>
       </c>
       <c r="C57" s="2">
         <v>1.0</v>
@@ -1431,10 +1431,10 @@
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="2">
-        <v>9.0</v>
+        <v>15.0</v>
       </c>
       <c r="B58" s="3">
-        <v>46287.66458333333</v>
+        <v>46294.53958333333</v>
       </c>
       <c r="C58" s="2">
         <v>1.0</v>
@@ -1454,7 +1454,7 @@
         <v>15.0</v>
       </c>
       <c r="B59" s="3">
-        <v>46287.743055555555</v>
+        <v>46294.53958333333</v>
       </c>
       <c r="C59" s="2">
         <v>1.0</v>
@@ -1471,10 +1471,10 @@
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="2">
-        <v>1.0</v>
+        <v>19.0</v>
       </c>
       <c r="B60" s="3">
-        <v>46287.82708333333</v>
+        <v>46294.56527777778</v>
       </c>
       <c r="C60" s="2">
         <v>1.0</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="2">
-        <v>13.0</v>
+        <v>7.0</v>
       </c>
       <c r="B61" s="3">
-        <v>46287.84583333333</v>
+        <v>46294.57430555556</v>
       </c>
       <c r="C61" s="2">
         <v>1.0</v>
@@ -1511,16 +1511,16 @@
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="2">
-        <v>10.0</v>
+        <v>17.0</v>
       </c>
       <c r="B62" s="3">
-        <v>46288.29375</v>
+        <v>46294.583333333336</v>
       </c>
       <c r="C62" s="2">
         <v>1.0</v>
       </c>
       <c r="D62" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="E62" s="2">
         <v>1.0</v>
@@ -1531,10 +1531,10 @@
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="2">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
       <c r="B63" s="3">
-        <v>46288.31319444445</v>
+        <v>46294.64027777778</v>
       </c>
       <c r="C63" s="2">
         <v>1.0</v>
@@ -1551,10 +1551,10 @@
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="2">
-        <v>6.0</v>
+        <v>15.0</v>
       </c>
       <c r="B64" s="3">
-        <v>46288.370833333334</v>
+        <v>46294.66111111111</v>
       </c>
       <c r="C64" s="2">
         <v>1.0</v>
@@ -1571,16 +1571,16 @@
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="2">
-        <v>17.0</v>
+        <v>11.0</v>
       </c>
       <c r="B65" s="3">
-        <v>46288.39236111111</v>
+        <v>46294.666666666664</v>
       </c>
       <c r="C65" s="2">
         <v>1.0</v>
       </c>
       <c r="D65" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="E65" s="2">
         <v>1.0</v>
@@ -1591,10 +1591,10 @@
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="2">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
       <c r="B66" s="3">
-        <v>46288.40277777778</v>
+        <v>46294.669444444444</v>
       </c>
       <c r="C66" s="2">
         <v>1.0</v>
@@ -1611,10 +1611,10 @@
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="2">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="B67" s="3">
-        <v>46288.40416666667</v>
+        <v>46294.67083333333</v>
       </c>
       <c r="C67" s="2">
         <v>1.0</v>
@@ -1631,16 +1631,16 @@
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="2">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="B68" s="3">
-        <v>46288.40416666667</v>
+        <v>46294.709027777775</v>
       </c>
       <c r="C68" s="2">
         <v>1.0</v>
       </c>
       <c r="D68" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="E68" s="2">
         <v>1.0</v>
@@ -1651,16 +1651,16 @@
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="2">
-        <v>19.0</v>
+        <v>13.0</v>
       </c>
       <c r="B69" s="3">
-        <v>46288.41111111111</v>
+        <v>46294.854166666664</v>
       </c>
       <c r="C69" s="2">
         <v>1.0</v>
       </c>
       <c r="D69" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="E69" s="2">
         <v>1.0</v>
@@ -1671,10 +1671,10 @@
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="2">
-        <v>15.0</v>
+        <v>10.0</v>
       </c>
       <c r="B70" s="3">
-        <v>46288.41388888889</v>
+        <v>46295.27638888889</v>
       </c>
       <c r="C70" s="2">
         <v>1.0</v>
@@ -1691,10 +1691,10 @@
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="2">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="B71" s="3">
-        <v>46288.42083333333</v>
+        <v>46295.277083333334</v>
       </c>
       <c r="C71" s="2">
         <v>1.0</v>
@@ -1711,16 +1711,16 @@
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="2">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="B72" s="3">
-        <v>46288.450694444444</v>
+        <v>46295.31736111111</v>
       </c>
       <c r="C72" s="2">
         <v>1.0</v>
       </c>
       <c r="D72" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="E72" s="2">
         <v>1.0</v>
@@ -1731,16 +1731,16 @@
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="2">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="B73" s="3">
-        <v>46288.47222222222</v>
+        <v>46295.379166666666</v>
       </c>
       <c r="C73" s="2">
         <v>1.0</v>
       </c>
       <c r="D73" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="E73" s="2">
         <v>1.0</v>
@@ -1751,16 +1751,16 @@
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="2">
-        <v>1.0</v>
+        <v>17.0</v>
       </c>
       <c r="B74" s="3">
-        <v>46288.47222222222</v>
+        <v>46295.39513888889</v>
       </c>
       <c r="C74" s="2">
         <v>1.0</v>
       </c>
       <c r="D74" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="E74" s="2">
         <v>1.0</v>
@@ -1771,16 +1771,16 @@
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="2">
-        <v>9.0</v>
+        <v>19.0</v>
       </c>
       <c r="B75" s="3">
-        <v>46288.47361111111</v>
+        <v>46295.41180555556</v>
       </c>
       <c r="C75" s="2">
         <v>1.0</v>
       </c>
       <c r="D75" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="E75" s="2">
         <v>1.0</v>
@@ -1791,16 +1791,16 @@
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="2">
-        <v>19.0</v>
+        <v>5.0</v>
       </c>
       <c r="B76" s="3">
-        <v>46288.47430555556</v>
+        <v>46295.41388888889</v>
       </c>
       <c r="C76" s="2">
         <v>1.0</v>
       </c>
       <c r="D76" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="E76" s="2">
         <v>1.0</v>
@@ -1814,7 +1814,7 @@
         <v>5.0</v>
       </c>
       <c r="B77" s="3">
-        <v>46288.49652777778</v>
+        <v>46295.41388888889</v>
       </c>
       <c r="C77" s="2">
         <v>1.0</v>
@@ -1834,13 +1834,13 @@
         <v>6.0</v>
       </c>
       <c r="B78" s="3">
-        <v>46288.535416666666</v>
+        <v>46295.41388888889</v>
       </c>
       <c r="C78" s="2">
         <v>1.0</v>
       </c>
       <c r="D78" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="E78" s="2">
         <v>1.0</v>
@@ -1851,10 +1851,10 @@
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="2">
-        <v>3.0</v>
+        <v>15.0</v>
       </c>
       <c r="B79" s="3">
-        <v>46288.54236111111</v>
+        <v>46295.41875</v>
       </c>
       <c r="C79" s="2">
         <v>1.0</v>
@@ -1871,16 +1871,16 @@
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="2">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
       <c r="B80" s="3">
-        <v>46288.54791666667</v>
+        <v>46295.458333333336</v>
       </c>
       <c r="C80" s="2">
         <v>1.0</v>
       </c>
       <c r="D80" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="E80" s="2">
         <v>1.0</v>
@@ -1891,16 +1891,16 @@
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="2">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
       <c r="B81" s="3">
-        <v>46288.54861111111</v>
+        <v>46295.48333333333</v>
       </c>
       <c r="C81" s="2">
         <v>1.0</v>
       </c>
       <c r="D81" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="E81" s="2">
         <v>1.0</v>
@@ -1911,16 +1911,16 @@
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="2">
-        <v>15.0</v>
+        <v>11.0</v>
       </c>
       <c r="B82" s="3">
-        <v>46288.57430555556</v>
+        <v>46295.509722222225</v>
       </c>
       <c r="C82" s="2">
         <v>1.0</v>
       </c>
       <c r="D82" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="E82" s="2">
         <v>1.0</v>
@@ -1931,10 +1931,10 @@
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="2">
-        <v>15.0</v>
+        <v>5.0</v>
       </c>
       <c r="B83" s="3">
-        <v>46288.57430555556</v>
+        <v>46295.54375</v>
       </c>
       <c r="C83" s="2">
         <v>1.0</v>
@@ -1951,16 +1951,16 @@
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="2">
-        <v>17.0</v>
+        <v>12.0</v>
       </c>
       <c r="B84" s="3">
-        <v>46288.595138888886</v>
+        <v>46295.552777777775</v>
       </c>
       <c r="C84" s="2">
         <v>1.0</v>
       </c>
       <c r="D84" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="E84" s="2">
         <v>1.0</v>
@@ -1971,16 +1971,16 @@
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="2">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="B85" s="3">
-        <v>46288.59583333333</v>
+        <v>46295.555555555555</v>
       </c>
       <c r="C85" s="2">
         <v>1.0</v>
       </c>
       <c r="D85" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="E85" s="2">
         <v>1.0</v>
@@ -1991,16 +1991,16 @@
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="2">
-        <v>7.0</v>
+        <v>15.0</v>
       </c>
       <c r="B86" s="3">
-        <v>46288.59583333333</v>
+        <v>46295.58125</v>
       </c>
       <c r="C86" s="2">
         <v>1.0</v>
       </c>
       <c r="D86" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="E86" s="2">
         <v>1.0</v>
@@ -2011,10 +2011,10 @@
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="2">
-        <v>6.0</v>
+        <v>17.0</v>
       </c>
       <c r="B87" s="3">
-        <v>46288.59652777778</v>
+        <v>46295.586805555555</v>
       </c>
       <c r="C87" s="2">
         <v>1.0</v>
@@ -2031,10 +2031,10 @@
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="2">
-        <v>13.0</v>
+        <v>7.0</v>
       </c>
       <c r="B88" s="3">
-        <v>46288.63611111111</v>
+        <v>46295.60277777778</v>
       </c>
       <c r="C88" s="2">
         <v>1.0</v>
@@ -2051,16 +2051,16 @@
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="2">
-        <v>13.0</v>
+        <v>11.0</v>
       </c>
       <c r="B89" s="3">
-        <v>46288.63888888889</v>
+        <v>46295.60486111111</v>
       </c>
       <c r="C89" s="2">
         <v>1.0</v>
       </c>
       <c r="D89" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="E89" s="2">
         <v>1.0</v>
@@ -2071,16 +2071,16 @@
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="2">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="B90" s="3">
-        <v>46288.65694444445</v>
+        <v>46295.60625</v>
       </c>
       <c r="C90" s="2">
         <v>1.0</v>
       </c>
       <c r="D90" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="E90" s="2">
         <v>1.0</v>
@@ -2091,10 +2091,10 @@
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="2">
-        <v>5.0</v>
+        <v>13.0</v>
       </c>
       <c r="B91" s="3">
-        <v>46288.65902777778</v>
+        <v>46295.64166666667</v>
       </c>
       <c r="C91" s="2">
         <v>1.0</v>
@@ -2111,10 +2111,10 @@
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="2">
-        <v>19.0</v>
+        <v>2.0</v>
       </c>
       <c r="B92" s="3">
-        <v>46288.66180555556</v>
+        <v>46295.663194444445</v>
       </c>
       <c r="C92" s="2">
         <v>1.0</v>
@@ -2131,16 +2131,16 @@
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="2">
-        <v>1.0</v>
+        <v>19.0</v>
       </c>
       <c r="B93" s="3">
-        <v>46288.66527777778</v>
+        <v>46295.665972222225</v>
       </c>
       <c r="C93" s="2">
         <v>1.0</v>
       </c>
       <c r="D93" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="E93" s="2">
         <v>1.0</v>
@@ -2151,16 +2151,16 @@
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="2">
-        <v>6.0</v>
+        <v>19.0</v>
       </c>
       <c r="B94" s="3">
-        <v>46288.67569444444</v>
+        <v>46295.666666666664</v>
       </c>
       <c r="C94" s="2">
         <v>1.0</v>
       </c>
       <c r="D94" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="E94" s="2">
         <v>1.0</v>
@@ -2171,16 +2171,16 @@
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="2">
-        <v>5.0</v>
+        <v>19.0</v>
       </c>
       <c r="B95" s="3">
-        <v>46288.71666666667</v>
+        <v>46295.666666666664</v>
       </c>
       <c r="C95" s="2">
         <v>1.0</v>
       </c>
       <c r="D95" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="E95" s="2">
         <v>1.0</v>
@@ -2191,16 +2191,16 @@
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="2">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="B96" s="3">
-        <v>46288.720138888886</v>
+        <v>46295.67152777778</v>
       </c>
       <c r="C96" s="2">
         <v>1.0</v>
       </c>
       <c r="D96" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="E96" s="2">
         <v>1.0</v>
@@ -2211,16 +2211,16 @@
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="2">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="B97" s="3">
-        <v>46288.722916666666</v>
+        <v>46295.67222222222</v>
       </c>
       <c r="C97" s="2">
         <v>1.0</v>
       </c>
       <c r="D97" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="E97" s="2">
         <v>1.0</v>
@@ -2231,16 +2231,16 @@
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="2">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="B98" s="3">
-        <v>46288.72986111111</v>
+        <v>46295.675</v>
       </c>
       <c r="C98" s="2">
         <v>1.0</v>
       </c>
       <c r="D98" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="E98" s="2">
         <v>1.0</v>
@@ -2251,10 +2251,10 @@
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="2">
-        <v>7.0</v>
+        <v>12.0</v>
       </c>
       <c r="B99" s="3">
-        <v>46288.76875</v>
+        <v>46295.729166666664</v>
       </c>
       <c r="C99" s="2">
         <v>1.0</v>
@@ -2271,10 +2271,10 @@
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="2">
-        <v>19.0</v>
+        <v>12.0</v>
       </c>
       <c r="B100" s="3">
-        <v>46288.788194444445</v>
+        <v>46295.729166666664</v>
       </c>
       <c r="C100" s="2">
         <v>1.0</v>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="2">
-        <v>2.0</v>
+        <v>11.0</v>
       </c>
       <c r="B101" s="3">
-        <v>46288.82638888889</v>
+        <v>46295.743055555555</v>
       </c>
       <c r="C101" s="2">
         <v>1.0</v>
@@ -2311,10 +2311,10 @@
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="2">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="B102" s="3">
-        <v>46288.82708333333</v>
+        <v>46295.771527777775</v>
       </c>
       <c r="C102" s="2">
         <v>1.0</v>
@@ -2334,7 +2334,7 @@
         <v>19.0</v>
       </c>
       <c r="B103" s="3">
-        <v>46288.83819444444</v>
+        <v>46295.78888888889</v>
       </c>
       <c r="C103" s="2">
         <v>1.0</v>
@@ -2351,16 +2351,16 @@
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="B104" s="3">
-        <v>46289.26666666667</v>
+        <v>46295.79027777778</v>
       </c>
       <c r="C104" s="2">
         <v>1.0</v>
       </c>
       <c r="D104" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="E104" s="2">
         <v>1.0</v>
@@ -2371,16 +2371,16 @@
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="2">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="B105" s="3">
-        <v>46289.26736111111</v>
+        <v>46295.83263888889</v>
       </c>
       <c r="C105" s="2">
         <v>1.0</v>
       </c>
       <c r="D105" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="E105" s="2">
         <v>1.0</v>
@@ -2391,16 +2391,16 @@
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="2">
-        <v>12.0</v>
+        <v>2.0</v>
       </c>
       <c r="B106" s="3">
-        <v>46289.279861111114</v>
+        <v>46295.833333333336</v>
       </c>
       <c r="C106" s="2">
         <v>1.0</v>
       </c>
       <c r="D106" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="E106" s="2">
         <v>1.0</v>
@@ -2411,16 +2411,16 @@
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="2">
-        <v>17.0</v>
+        <v>1.0</v>
       </c>
       <c r="B107" s="3">
-        <v>46289.294444444444</v>
+        <v>46295.8375</v>
       </c>
       <c r="C107" s="2">
         <v>1.0</v>
       </c>
       <c r="D107" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="E107" s="2">
         <v>1.0</v>
@@ -2431,16 +2431,16 @@
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="2">
-        <v>19.0</v>
+        <v>13.0</v>
       </c>
       <c r="B108" s="3">
-        <v>46289.33541666667</v>
+        <v>46295.85486111111</v>
       </c>
       <c r="C108" s="2">
         <v>1.0</v>
       </c>
       <c r="D108" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="E108" s="2">
         <v>1.0</v>
@@ -2451,16 +2451,16 @@
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="2">
-        <v>7.0</v>
+        <v>13.0</v>
       </c>
       <c r="B109" s="3">
-        <v>46289.342361111114</v>
+        <v>46295.85555555556</v>
       </c>
       <c r="C109" s="2">
         <v>1.0</v>
       </c>
       <c r="D109" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="E109" s="2">
         <v>1.0</v>
@@ -2471,10 +2471,10 @@
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="B110" s="3">
-        <v>46289.37291666667</v>
+        <v>46296.27777777778</v>
       </c>
       <c r="C110" s="2">
         <v>1.0</v>
@@ -2491,16 +2491,16 @@
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="2">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
       <c r="B111" s="3">
-        <v>46289.404861111114</v>
+        <v>46296.288194444445</v>
       </c>
       <c r="C111" s="2">
         <v>1.0</v>
       </c>
       <c r="D111" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="E111" s="2">
         <v>1.0</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="2">
-        <v>5.0</v>
+        <v>12.0</v>
       </c>
       <c r="B112" s="3">
-        <v>46289.40833333333</v>
+        <v>46296.288194444445</v>
       </c>
       <c r="C112" s="2">
         <v>1.0</v>
@@ -2531,10 +2531,10 @@
     </row>
     <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="2">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="B113" s="3">
-        <v>46289.40972222222</v>
+        <v>46296.29027777778</v>
       </c>
       <c r="C113" s="2">
         <v>1.0</v>
@@ -2551,10 +2551,10 @@
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="2">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="B114" s="3">
-        <v>46289.44861111111</v>
+        <v>46296.34305555555</v>
       </c>
       <c r="C114" s="2">
         <v>1.0</v>
@@ -2571,16 +2571,16 @@
     </row>
     <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="2">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="B115" s="3">
-        <v>46289.46111111111</v>
+        <v>46296.35</v>
       </c>
       <c r="C115" s="2">
         <v>1.0</v>
       </c>
       <c r="D115" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="E115" s="2">
         <v>1.0</v>
@@ -2591,16 +2591,16 @@
     </row>
     <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="2">
-        <v>6.0</v>
+        <v>19.0</v>
       </c>
       <c r="B116" s="3">
-        <v>46289.47361111111</v>
+        <v>46296.375</v>
       </c>
       <c r="C116" s="2">
         <v>1.0</v>
       </c>
       <c r="D116" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="E116" s="2">
         <v>1.0</v>
@@ -2611,16 +2611,16 @@
     </row>
     <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="B117" s="4">
-        <v>46289.479166666664</v>
+        <v>46296.38125</v>
       </c>
       <c r="C117" s="2">
         <v>1.0</v>
       </c>
       <c r="D117" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="E117" s="2">
         <v>1.0</v>
@@ -2631,16 +2631,16 @@
     </row>
     <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="2">
-        <v>12.0</v>
+        <v>19.0</v>
       </c>
       <c r="B118" s="4">
-        <v>46289.47986111111</v>
+        <v>46296.41458333333</v>
       </c>
       <c r="C118" s="2">
         <v>1.0</v>
       </c>
       <c r="D118" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="E118" s="2">
         <v>1.0</v>
@@ -2651,16 +2651,16 @@
     </row>
     <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="2">
-        <v>19.0</v>
+        <v>9.0</v>
       </c>
       <c r="B119" s="4">
-        <v>46289.49444444444</v>
+        <v>46296.41458333333</v>
       </c>
       <c r="C119" s="2">
         <v>1.0</v>
       </c>
       <c r="D119" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="E119" s="2">
         <v>1.0</v>
@@ -2671,10 +2671,10 @@
     </row>
     <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="2">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
       <c r="B120" s="4">
-        <v>46289.49513888889</v>
+        <v>46296.41875</v>
       </c>
       <c r="C120" s="2">
         <v>1.0</v>
@@ -2691,16 +2691,16 @@
     </row>
     <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="2">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="B121" s="4">
-        <v>46289.50902777778</v>
+        <v>46296.45694444444</v>
       </c>
       <c r="C121" s="2">
         <v>1.0</v>
       </c>
       <c r="D121" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="E121" s="2">
         <v>1.0</v>
@@ -2711,16 +2711,16 @@
     </row>
     <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="2">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="B122" s="4">
-        <v>46289.509722222225</v>
+        <v>46296.458333333336</v>
       </c>
       <c r="C122" s="2">
         <v>1.0</v>
       </c>
       <c r="D122" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="E122" s="2">
         <v>1.0</v>
@@ -2731,16 +2731,16 @@
     </row>
     <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="2">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="B123" s="4">
-        <v>46289.552777777775</v>
+        <v>46296.458333333336</v>
       </c>
       <c r="C123" s="2">
         <v>1.0</v>
       </c>
       <c r="D123" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="E123" s="2">
         <v>1.0</v>
@@ -2751,16 +2751,16 @@
     </row>
     <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="2">
-        <v>3.0</v>
+        <v>17.0</v>
       </c>
       <c r="B124" s="4">
-        <v>46289.57430555556</v>
+        <v>46296.459027777775</v>
       </c>
       <c r="C124" s="2">
         <v>1.0</v>
       </c>
       <c r="D124" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="E124" s="2">
         <v>1.0</v>
@@ -2771,16 +2771,16 @@
     </row>
     <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="2">
-        <v>15.0</v>
+        <v>6.0</v>
       </c>
       <c r="B125" s="4">
-        <v>46289.575</v>
+        <v>46296.47777777778</v>
       </c>
       <c r="C125" s="2">
         <v>1.0</v>
       </c>
       <c r="D125" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="E125" s="2">
         <v>1.0</v>
@@ -2790,964 +2790,388 @@
       </c>
     </row>
     <row r="126" ht="15.75" customHeight="1">
-      <c r="A126" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="B126" s="4">
-        <v>46289.59652777778</v>
-      </c>
-      <c r="C126" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D126" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E126" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F126" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A126" s="2"/>
+      <c r="B126" s="4"/>
+      <c r="C126" s="2"/>
+      <c r="D126" s="2"/>
+      <c r="E126" s="2"/>
+      <c r="F126" s="2"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
-      <c r="A127" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="B127" s="4">
-        <v>46289.60138888889</v>
-      </c>
-      <c r="C127" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D127" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E127" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F127" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A127" s="2"/>
+      <c r="B127" s="4"/>
+      <c r="C127" s="2"/>
+      <c r="D127" s="2"/>
+      <c r="E127" s="2"/>
+      <c r="F127" s="2"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
-      <c r="A128" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="B128" s="4">
-        <v>46289.61875</v>
-      </c>
-      <c r="C128" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D128" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E128" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F128" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A128" s="2"/>
+      <c r="B128" s="4"/>
+      <c r="C128" s="2"/>
+      <c r="D128" s="2"/>
+      <c r="E128" s="2"/>
+      <c r="F128" s="2"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="A129" s="2">
-        <v>13.0</v>
-      </c>
-      <c r="B129" s="4">
-        <v>46289.63611111111</v>
-      </c>
-      <c r="C129" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D129" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E129" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F129" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A129" s="2"/>
+      <c r="B129" s="4"/>
+      <c r="C129" s="2"/>
+      <c r="D129" s="2"/>
+      <c r="E129" s="2"/>
+      <c r="F129" s="2"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="A130" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="B130" s="4">
-        <v>46289.63680555556</v>
-      </c>
-      <c r="C130" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D130" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E130" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F130" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A130" s="2"/>
+      <c r="B130" s="4"/>
+      <c r="C130" s="2"/>
+      <c r="D130" s="2"/>
+      <c r="E130" s="2"/>
+      <c r="F130" s="2"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="A131" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="B131" s="4">
-        <v>46289.665972222225</v>
-      </c>
-      <c r="C131" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D131" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E131" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F131" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A131" s="2"/>
+      <c r="B131" s="4"/>
+      <c r="C131" s="2"/>
+      <c r="D131" s="2"/>
+      <c r="E131" s="2"/>
+      <c r="F131" s="2"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
-      <c r="A132" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="B132" s="4">
-        <v>46289.66736111111</v>
-      </c>
-      <c r="C132" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D132" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E132" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F132" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A132" s="2"/>
+      <c r="B132" s="4"/>
+      <c r="C132" s="2"/>
+      <c r="D132" s="2"/>
+      <c r="E132" s="2"/>
+      <c r="F132" s="2"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
-      <c r="A133" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="B133" s="4">
-        <v>46289.768055555556</v>
-      </c>
-      <c r="C133" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D133" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E133" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F133" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A133" s="2"/>
+      <c r="B133" s="4"/>
+      <c r="C133" s="2"/>
+      <c r="D133" s="2"/>
+      <c r="E133" s="2"/>
+      <c r="F133" s="2"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
-      <c r="A134" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="B134" s="4">
-        <v>46289.82777777778</v>
-      </c>
-      <c r="C134" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D134" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E134" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F134" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A134" s="2"/>
+      <c r="B134" s="4"/>
+      <c r="C134" s="2"/>
+      <c r="D134" s="2"/>
+      <c r="E134" s="2"/>
+      <c r="F134" s="2"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
-      <c r="A135" s="2">
-        <v>13.0</v>
-      </c>
-      <c r="B135" s="4">
-        <v>46289.84722222222</v>
-      </c>
-      <c r="C135" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D135" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E135" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F135" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A135" s="2"/>
+      <c r="B135" s="4"/>
+      <c r="C135" s="2"/>
+      <c r="D135" s="2"/>
+      <c r="E135" s="2"/>
+      <c r="F135" s="2"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
-      <c r="A136" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="B136" s="4">
-        <v>46290.27222222222</v>
-      </c>
-      <c r="C136" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D136" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E136" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F136" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A136" s="2"/>
+      <c r="B136" s="4"/>
+      <c r="C136" s="2"/>
+      <c r="D136" s="2"/>
+      <c r="E136" s="2"/>
+      <c r="F136" s="2"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
-      <c r="A137" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="B137" s="4">
-        <v>46290.311111111114</v>
-      </c>
-      <c r="C137" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D137" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E137" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F137" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A137" s="2"/>
+      <c r="B137" s="4"/>
+      <c r="C137" s="2"/>
+      <c r="D137" s="2"/>
+      <c r="E137" s="2"/>
+      <c r="F137" s="2"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
-      <c r="A138" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="B138" s="4">
-        <v>46290.35902777778</v>
-      </c>
-      <c r="C138" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D138" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E138" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F138" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A138" s="2"/>
+      <c r="B138" s="4"/>
+      <c r="C138" s="2"/>
+      <c r="D138" s="2"/>
+      <c r="E138" s="2"/>
+      <c r="F138" s="2"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
-      <c r="A139" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="B139" s="4">
-        <v>46290.36875</v>
-      </c>
-      <c r="C139" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D139" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E139" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F139" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A139" s="2"/>
+      <c r="B139" s="4"/>
+      <c r="C139" s="2"/>
+      <c r="D139" s="2"/>
+      <c r="E139" s="2"/>
+      <c r="F139" s="2"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="A140" s="2">
-        <v>15.0</v>
-      </c>
-      <c r="B140" s="4">
-        <v>46290.393055555556</v>
-      </c>
-      <c r="C140" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D140" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E140" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F140" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A140" s="2"/>
+      <c r="B140" s="4"/>
+      <c r="C140" s="2"/>
+      <c r="D140" s="2"/>
+      <c r="E140" s="2"/>
+      <c r="F140" s="2"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
-      <c r="A141" s="2">
-        <v>17.0</v>
-      </c>
-      <c r="B141" s="4">
-        <v>46290.40347222222</v>
-      </c>
-      <c r="C141" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D141" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E141" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F141" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A141" s="2"/>
+      <c r="B141" s="4"/>
+      <c r="C141" s="2"/>
+      <c r="D141" s="2"/>
+      <c r="E141" s="2"/>
+      <c r="F141" s="2"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
-      <c r="A142" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="B142" s="4">
-        <v>46290.40694444445</v>
-      </c>
-      <c r="C142" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D142" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E142" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F142" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A142" s="2"/>
+      <c r="B142" s="4"/>
+      <c r="C142" s="2"/>
+      <c r="D142" s="2"/>
+      <c r="E142" s="2"/>
+      <c r="F142" s="2"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
-      <c r="A143" s="2">
-        <v>19.0</v>
-      </c>
-      <c r="B143" s="4">
-        <v>46290.41458333333</v>
-      </c>
-      <c r="C143" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D143" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E143" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F143" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A143" s="2"/>
+      <c r="B143" s="4"/>
+      <c r="C143" s="2"/>
+      <c r="D143" s="2"/>
+      <c r="E143" s="2"/>
+      <c r="F143" s="2"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="A144" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="B144" s="4">
-        <v>46290.45138888889</v>
-      </c>
-      <c r="C144" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D144" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E144" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F144" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A144" s="2"/>
+      <c r="B144" s="4"/>
+      <c r="C144" s="2"/>
+      <c r="D144" s="2"/>
+      <c r="E144" s="2"/>
+      <c r="F144" s="2"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
-      <c r="A145" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="B145" s="4">
-        <v>46290.46597222222</v>
-      </c>
-      <c r="C145" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D145" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E145" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F145" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A145" s="2"/>
+      <c r="B145" s="4"/>
+      <c r="C145" s="2"/>
+      <c r="D145" s="2"/>
+      <c r="E145" s="2"/>
+      <c r="F145" s="2"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="A146" s="2">
-        <v>19.0</v>
-      </c>
-      <c r="B146" s="4">
-        <v>46290.513194444444</v>
-      </c>
-      <c r="C146" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D146" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E146" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F146" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A146" s="2"/>
+      <c r="B146" s="4"/>
+      <c r="C146" s="2"/>
+      <c r="D146" s="2"/>
+      <c r="E146" s="2"/>
+      <c r="F146" s="2"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
-      <c r="A147" s="2">
-        <v>19.0</v>
-      </c>
-      <c r="B147" s="4">
-        <v>46290.51736111111</v>
-      </c>
-      <c r="C147" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D147" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E147" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F147" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A147" s="2"/>
+      <c r="B147" s="4"/>
+      <c r="C147" s="2"/>
+      <c r="D147" s="2"/>
+      <c r="E147" s="2"/>
+      <c r="F147" s="2"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="A148" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="B148" s="4">
-        <v>46290.52916666667</v>
-      </c>
-      <c r="C148" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D148" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E148" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F148" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A148" s="2"/>
+      <c r="B148" s="4"/>
+      <c r="C148" s="2"/>
+      <c r="D148" s="2"/>
+      <c r="E148" s="2"/>
+      <c r="F148" s="2"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="A149" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="B149" s="4">
-        <v>46290.53333333333</v>
-      </c>
-      <c r="C149" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D149" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E149" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F149" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A149" s="2"/>
+      <c r="B149" s="4"/>
+      <c r="C149" s="2"/>
+      <c r="D149" s="2"/>
+      <c r="E149" s="2"/>
+      <c r="F149" s="2"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="B150" s="4">
-        <v>46290.540972222225</v>
-      </c>
-      <c r="C150" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D150" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E150" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F150" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A150" s="2"/>
+      <c r="B150" s="4"/>
+      <c r="C150" s="2"/>
+      <c r="D150" s="2"/>
+      <c r="E150" s="2"/>
+      <c r="F150" s="2"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
-      <c r="A151" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="B151" s="4">
-        <v>46290.549305555556</v>
-      </c>
-      <c r="C151" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D151" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E151" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F151" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A151" s="2"/>
+      <c r="B151" s="4"/>
+      <c r="C151" s="2"/>
+      <c r="D151" s="2"/>
+      <c r="E151" s="2"/>
+      <c r="F151" s="2"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="A152" s="2">
-        <v>12.0</v>
-      </c>
-      <c r="B152" s="4">
-        <v>46290.552083333336</v>
-      </c>
-      <c r="C152" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D152" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E152" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F152" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A152" s="2"/>
+      <c r="B152" s="4"/>
+      <c r="C152" s="2"/>
+      <c r="D152" s="2"/>
+      <c r="E152" s="2"/>
+      <c r="F152" s="2"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
-      <c r="A153" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="B153" s="4">
-        <v>46290.56458333333</v>
-      </c>
-      <c r="C153" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D153" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E153" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F153" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A153" s="2"/>
+      <c r="B153" s="4"/>
+      <c r="C153" s="2"/>
+      <c r="D153" s="2"/>
+      <c r="E153" s="2"/>
+      <c r="F153" s="2"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
-      <c r="A154" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="B154" s="4">
-        <v>46290.56597222222</v>
-      </c>
-      <c r="C154" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D154" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E154" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F154" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A154" s="2"/>
+      <c r="B154" s="4"/>
+      <c r="C154" s="2"/>
+      <c r="D154" s="2"/>
+      <c r="E154" s="2"/>
+      <c r="F154" s="2"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="A155" s="2">
-        <v>15.0</v>
-      </c>
-      <c r="B155" s="4">
-        <v>46290.575694444444</v>
-      </c>
-      <c r="C155" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D155" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E155" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F155" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A155" s="2"/>
+      <c r="B155" s="4"/>
+      <c r="C155" s="2"/>
+      <c r="D155" s="2"/>
+      <c r="E155" s="2"/>
+      <c r="F155" s="2"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="A156" s="2">
-        <v>17.0</v>
-      </c>
-      <c r="B156" s="4">
-        <v>46290.57708333333</v>
-      </c>
-      <c r="C156" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D156" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E156" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F156" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A156" s="2"/>
+      <c r="B156" s="4"/>
+      <c r="C156" s="2"/>
+      <c r="D156" s="2"/>
+      <c r="E156" s="2"/>
+      <c r="F156" s="2"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
-      <c r="A157" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="B157" s="4">
-        <v>46290.57986111111</v>
-      </c>
-      <c r="C157" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D157" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E157" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F157" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A157" s="2"/>
+      <c r="B157" s="4"/>
+      <c r="C157" s="2"/>
+      <c r="D157" s="2"/>
+      <c r="E157" s="2"/>
+      <c r="F157" s="2"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
-      <c r="A158" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="B158" s="4">
-        <v>46290.59166666667</v>
-      </c>
-      <c r="C158" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D158" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E158" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F158" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A158" s="2"/>
+      <c r="B158" s="4"/>
+      <c r="C158" s="2"/>
+      <c r="D158" s="2"/>
+      <c r="E158" s="2"/>
+      <c r="F158" s="2"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
-      <c r="A159" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="B159" s="4">
-        <v>46290.59166666667</v>
-      </c>
-      <c r="C159" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D159" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E159" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F159" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A159" s="2"/>
+      <c r="B159" s="4"/>
+      <c r="C159" s="2"/>
+      <c r="D159" s="2"/>
+      <c r="E159" s="2"/>
+      <c r="F159" s="2"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
-      <c r="A160" s="2">
-        <v>13.0</v>
-      </c>
-      <c r="B160" s="4">
-        <v>46290.63958333333</v>
-      </c>
-      <c r="C160" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D160" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E160" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F160" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A160" s="2"/>
+      <c r="B160" s="4"/>
+      <c r="C160" s="2"/>
+      <c r="D160" s="2"/>
+      <c r="E160" s="2"/>
+      <c r="F160" s="2"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
-      <c r="A161" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="B161" s="4">
-        <v>46290.65902777778</v>
-      </c>
-      <c r="C161" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D161" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E161" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F161" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A161" s="2"/>
+      <c r="B161" s="4"/>
+      <c r="C161" s="2"/>
+      <c r="D161" s="2"/>
+      <c r="E161" s="2"/>
+      <c r="F161" s="2"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
-      <c r="A162" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="B162" s="4">
-        <v>46290.66527777778</v>
-      </c>
-      <c r="C162" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D162" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E162" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F162" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A162" s="2"/>
+      <c r="B162" s="4"/>
+      <c r="C162" s="2"/>
+      <c r="D162" s="2"/>
+      <c r="E162" s="2"/>
+      <c r="F162" s="2"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
-      <c r="A163" s="2">
-        <v>19.0</v>
-      </c>
-      <c r="B163" s="4">
-        <v>46290.67291666667</v>
-      </c>
-      <c r="C163" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D163" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E163" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F163" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A163" s="2"/>
+      <c r="B163" s="4"/>
+      <c r="C163" s="2"/>
+      <c r="D163" s="2"/>
+      <c r="E163" s="2"/>
+      <c r="F163" s="2"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
-      <c r="A164" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="B164" s="4">
-        <v>46290.675</v>
-      </c>
-      <c r="C164" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D164" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E164" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F164" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A164" s="2"/>
+      <c r="B164" s="4"/>
+      <c r="C164" s="2"/>
+      <c r="D164" s="2"/>
+      <c r="E164" s="2"/>
+      <c r="F164" s="2"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
-      <c r="A165" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="B165" s="4">
-        <v>46290.717361111114</v>
-      </c>
-      <c r="C165" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D165" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E165" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F165" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A165" s="2"/>
+      <c r="B165" s="4"/>
+      <c r="C165" s="2"/>
+      <c r="D165" s="2"/>
+      <c r="E165" s="2"/>
+      <c r="F165" s="2"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
-      <c r="A166" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="B166" s="4">
-        <v>46290.717361111114</v>
-      </c>
-      <c r="C166" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D166" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E166" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F166" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A166" s="2"/>
+      <c r="B166" s="4"/>
+      <c r="C166" s="2"/>
+      <c r="D166" s="2"/>
+      <c r="E166" s="2"/>
+      <c r="F166" s="2"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
-      <c r="A167" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="B167" s="4">
-        <v>46290.71805555555</v>
-      </c>
-      <c r="C167" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D167" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E167" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F167" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A167" s="2"/>
+      <c r="B167" s="4"/>
+      <c r="C167" s="2"/>
+      <c r="D167" s="2"/>
+      <c r="E167" s="2"/>
+      <c r="F167" s="2"/>
     </row>
     <row r="168" ht="15.75" customHeight="1">
-      <c r="A168" s="2">
-        <v>12.0</v>
-      </c>
-      <c r="B168" s="4">
-        <v>46290.71944444445</v>
-      </c>
-      <c r="C168" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D168" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E168" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F168" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A168" s="2"/>
+      <c r="B168" s="4"/>
+      <c r="C168" s="2"/>
+      <c r="D168" s="2"/>
+      <c r="E168" s="2"/>
+      <c r="F168" s="2"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
-      <c r="A169" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="B169" s="4">
-        <v>46290.75</v>
-      </c>
-      <c r="C169" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D169" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E169" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F169" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A169" s="2"/>
+      <c r="B169" s="4"/>
+      <c r="C169" s="2"/>
+      <c r="D169" s="2"/>
+      <c r="E169" s="2"/>
+      <c r="F169" s="2"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
-      <c r="A170" s="2">
-        <v>19.0</v>
-      </c>
-      <c r="B170" s="4">
-        <v>46290.8</v>
-      </c>
-      <c r="C170" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D170" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E170" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F170" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A170" s="2"/>
+      <c r="B170" s="4"/>
+      <c r="C170" s="2"/>
+      <c r="D170" s="2"/>
+      <c r="E170" s="2"/>
+      <c r="F170" s="2"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
-      <c r="A171" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="B171" s="4">
-        <v>46290.82777777778</v>
-      </c>
-      <c r="C171" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D171" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E171" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F171" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A171" s="2"/>
+      <c r="B171" s="4"/>
+      <c r="C171" s="2"/>
+      <c r="D171" s="2"/>
+      <c r="E171" s="2"/>
+      <c r="F171" s="2"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
-      <c r="A172" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="B172" s="4">
-        <v>46290.83611111111</v>
-      </c>
-      <c r="C172" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D172" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E172" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F172" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A172" s="2"/>
+      <c r="B172" s="4"/>
+      <c r="C172" s="2"/>
+      <c r="D172" s="2"/>
+      <c r="E172" s="2"/>
+      <c r="F172" s="2"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
-      <c r="A173" s="2">
-        <v>13.0</v>
-      </c>
-      <c r="B173" s="4">
-        <v>46290.85625</v>
-      </c>
-      <c r="C173" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D173" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E173" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F173" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A173" s="2"/>
+      <c r="B173" s="4"/>
+      <c r="C173" s="2"/>
+      <c r="D173" s="2"/>
+      <c r="E173" s="2"/>
+      <c r="F173" s="2"/>
     </row>
     <row r="174" ht="15.75" customHeight="1"/>
     <row r="175" ht="15.75" customHeight="1"/>
